--- a/Assets/Resources/DataFiles/QuestData/1. ExcelFile/QuestLabel.xlsx
+++ b/Assets/Resources/DataFiles/QuestData/1. ExcelFile/QuestLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,30 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>크레딧 {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_kill</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>적 처치</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_collect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>물건 수집</t>
         </is>
       </c>
     </row>
@@ -946,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,6 +1486,30 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>{0} Credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_kill</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Defeat Enemies</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_collect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Collect Items</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1992,6 +2040,30 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>クレジット {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_kill</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>敵撃破</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_collect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>アイテム収集</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,6 +2597,30 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_kill</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>击败敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_collect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>收集物品</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/QuestData/1. ExcelFile/QuestLabel.xlsx
+++ b/Assets/Resources/DataFiles/QuestData/1. ExcelFile/QuestLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,66 @@
       <c r="B45" t="inlineStr">
         <is>
           <t>물건 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_completed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>목표 달성</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_pending</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>보상 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>수령 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>quest_ui.credit_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>크레딧</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received_message</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>'{0}' 의뢰 보상을 수령했습니다: {1}</t>
         </is>
       </c>
     </row>
@@ -970,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,6 +1570,66 @@
       <c r="B45" t="inlineStr">
         <is>
           <t>Collect Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_completed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Objective Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_pending</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Reward Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reward Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>quest_ui.credit_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received_message</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Received the reward for the '{0}' request: {1}</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2064,6 +2184,66 @@
       <c r="B45" t="inlineStr">
         <is>
           <t>アイテム収集</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_completed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>目標達成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_pending</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>報酬待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>受取済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>quest_ui.credit_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>クレジット</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received_message</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>「{0}」依頼の報酬を受け取りました: {1}</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2801,66 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>quest_ui.objective_completed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>目标达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_pending</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>待领取奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>已领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>quest_ui.credit_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>信用点</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>quest_ui.reward_received_message</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>已领取「{0}」委托的奖励：{1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
